--- a/AAII_Financials/Quarterly/MLLUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MLLUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>MLLUY</t>
   </si>
@@ -656,73 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -762,8 +771,17 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -803,8 +821,17 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,8 +871,17 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +897,11 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,8 +941,17 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,8 +991,17 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -984,8 +1041,17 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,8 +1091,17 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1039,8 +1114,11 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1080,8 +1158,17 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1121,8 +1208,17 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,8 +1234,11 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1179,8 +1278,17 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1220,8 +1328,17 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1261,8 +1378,17 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1302,8 +1428,17 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1343,8 +1478,17 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1384,8 +1528,17 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1425,8 +1578,17 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1466,8 +1628,17 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1507,8 +1678,17 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1548,8 +1728,17 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1589,8 +1778,17 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1630,8 +1828,17 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1671,8 +1878,17 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1712,8 +1928,17 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1753,8 +1978,17 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1794,54 +2028,72 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1857,8 +2109,11 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1874,49 +2129,61 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10022600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>12255300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>11118200</v>
+      </c>
+      <c r="G41" s="3">
         <v>7238000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>7406300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>6917600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>7200700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>4798600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>6549800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>6969200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>6267200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>7248800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>8563800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>8449600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>6594800</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1924,327 +2191,399 @@
         <v>300</v>
       </c>
       <c r="E42" s="3">
+        <v>300</v>
+      </c>
+      <c r="F42" s="3">
+        <v>300</v>
+      </c>
+      <c r="G42" s="3">
+        <v>300</v>
+      </c>
+      <c r="H42" s="3">
         <v>400</v>
-      </c>
-      <c r="F42" s="3">
-        <v>400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>300</v>
       </c>
       <c r="I42" s="3">
         <v>400</v>
       </c>
       <c r="J42" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K42" s="3">
         <v>300</v>
       </c>
       <c r="L42" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M42" s="3">
         <v>300</v>
       </c>
       <c r="N42" s="3">
+        <v>300</v>
+      </c>
+      <c r="O42" s="3">
+        <v>300</v>
+      </c>
+      <c r="P42" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="R42" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>73032900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>70212100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>74091600</v>
+      </c>
+      <c r="G43" s="3">
         <v>70110400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>67745100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>63721100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>59892500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>55611900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>55990300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>48169700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>44579600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>45480200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>43868700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>43110900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>38959000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2395900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2805000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2242900</v>
+      </c>
+      <c r="G44" s="3">
         <v>10049500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>10067000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>10256500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>10356500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>11381600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>11008300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>11348400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>11292700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>11884700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>11780900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>12547300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>11591500</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3811200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4455300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3680600</v>
+      </c>
+      <c r="G45" s="3">
         <v>4873600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>4147900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>4745900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
         <v>4365600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>5244300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>4945500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>6238100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>5800700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>5774000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>5497000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>6871500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="R45" s="3">
         <v>6062200</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>89262900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>89728000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>91449600</v>
+      </c>
+      <c r="G46" s="3">
         <v>92271800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>89784600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>85641500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>82170000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>77036700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>78873800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>72725600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>68275400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>70388000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>70141200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>70979800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>63533800</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6953100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6892100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>6704600</v>
+      </c>
+      <c r="G47" s="3">
         <v>6734400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>6627200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>6370900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>6117600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>5982700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>5713900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>5786100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>5832100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>5424100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>5368500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>5540800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="R47" s="3">
         <v>5405300</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3169000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3190500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3135000</v>
+      </c>
+      <c r="G48" s="3">
         <v>4727000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>4646800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>4584600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>4587600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>4530400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>4383700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>4425200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>4558600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>4101000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>4177700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>4351400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>4400100</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4079600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3932900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3809500</v>
+      </c>
+      <c r="G49" s="3">
         <v>4888900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>4759400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>4658000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>4616100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>3346400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>3224900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>3245900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>3229500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>3132800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>3112000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>3225800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>3201400</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2284,8 +2623,17 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2325,49 +2673,67 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11782400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>14623200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>11550300</v>
+      </c>
+      <c r="G52" s="3">
         <v>12713200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>11591500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>12174300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>11030200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>11280900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>10333400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>10241900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>10042400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>8737900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>7986200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>7577500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>7088500</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2407,49 +2773,67 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>118772000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>119674700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>120023000</v>
+      </c>
+      <c r="G54" s="3">
         <v>122627200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>119685900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>114661900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>110700700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>103358200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>103971600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>97374900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>93303000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>92699500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>92001500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>92614200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>84874000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2465,8 +2849,11 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2482,254 +2869,311 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>54984200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>57730800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>55868800</v>
+      </c>
+      <c r="G57" s="3">
         <v>55380900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>50077200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>49892200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>46271500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>43983000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>14336300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>38151600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>13112800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>36716000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>13883500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>34682700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>13169600</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4657100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5879300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5169700</v>
+      </c>
+      <c r="G58" s="3">
         <v>10201300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>10577600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>10769200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>6634200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>8207500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>9377200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>9087000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>5053600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>7225900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>6770600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>7181600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="R58" s="3">
         <v>4594900</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19390800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>20449200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>20769700</v>
+      </c>
+      <c r="G59" s="3">
         <v>22275200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>21201400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>21158500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>21365500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>18255100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>45986800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>18661600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>41547000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>18167000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>37266600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>17760900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>35349700</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>83622400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>84388400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>86700000</v>
+      </c>
+      <c r="G60" s="3">
         <v>88251000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>86226900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>82159900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>78589100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>70852500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>74113500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>66258300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>63295000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>62473400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>61245300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>59959800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>55942200</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7121200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7491200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>6270300</v>
+      </c>
+      <c r="G61" s="3">
         <v>7213900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>7217300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>7647200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>6128700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>5340500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>5498200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>5930700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>5354800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>5586000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>5676900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>5839100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>4452500</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>321700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>366300</v>
+      </c>
+      <c r="F62" s="3">
+        <v>332100</v>
+      </c>
+      <c r="G62" s="3">
         <v>416900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>409300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>445700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>371200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>351000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>317700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>299000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>309400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>365300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>290000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>394900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>312800</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2769,8 +3213,17 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2810,8 +3263,17 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2851,49 +3313,67 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91556100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>92718700</v>
+      </c>
+      <c r="F66" s="3">
+        <v>93779200</v>
+      </c>
+      <c r="G66" s="3">
         <v>96525500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>94475900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>90887500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>85720100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>77215000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>80570300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>73132000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>69611900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>69080100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>67863600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>66890200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>61398100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2909,8 +3389,11 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2950,8 +3433,17 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2991,8 +3483,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3032,8 +3533,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3073,49 +3583,67 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8248400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8220300</v>
+      </c>
+      <c r="F72" s="3">
+        <v>7873700</v>
+      </c>
+      <c r="G72" s="3">
         <v>8143900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>7971600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>7998800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>7738300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>8092900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>7441300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>7721800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>7509800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>7238000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>7149000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>7462100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>6971900</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3155,8 +3683,17 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3196,8 +3733,17 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3237,49 +3783,67 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23065600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>22803000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>22269600</v>
+      </c>
+      <c r="G76" s="3">
         <v>21914400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>21096200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>19789200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>20967400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>21936100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>20699900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>21068600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>20516500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>20144000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>19341600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>20703500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>17560200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3319,54 +3883,72 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3406,8 +3988,17 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3423,49 +4014,61 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>214700</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3">
         <v>-287600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>203700</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>405700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>-258500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>196600</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>429400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>-264300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>216800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>447500</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3505,8 +4108,17 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3546,8 +4158,17 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3587,8 +4208,17 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3628,8 +4258,17 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3669,49 +4308,67 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>333300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3634000</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3">
         <v>364400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>517800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-3540900</v>
       </c>
-      <c r="G89" s="3">
-        <v>5286000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>-332100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>322200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-4258300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>4000700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-1091000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>970900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-3138300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>2859500</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3727,49 +4384,61 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-167600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-128400</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
         <v>-67500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-166600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-113600</v>
       </c>
-      <c r="G91" s="3">
-        <v>-676300</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3">
         <v>-55700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-136300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-75400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-419100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-17600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-117900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-93300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="R91" s="3">
         <v>-361400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3809,8 +4478,17 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3850,49 +4528,67 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-403200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3661500</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
         <v>-108200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>198600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>-279400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-907700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>-179000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-141100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-93600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-473500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-116400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-161700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-195800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-447400</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3908,49 +4604,61 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>149300</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>374000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="H96" s="3">
         <v>175500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="I96" s="3">
         <v>252000</v>
       </c>
-      <c r="G96" s="3">
-        <v>225400</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>426200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="L96" s="3">
         <v>163100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="M96" s="3">
         <v>207500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="N96" s="3">
         <v>213200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="O96" s="3">
         <v>354500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="P96" s="3">
         <v>164200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="Q96" s="3">
         <v>160600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="R96" s="3">
         <v>409800</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3990,8 +4698,17 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4031,8 +4748,17 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4072,127 +4798,163 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2415800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>955500</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
         <v>-510900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>-186000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>3593000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1986900</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>-875700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-683300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>5078600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-4465200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>235100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-640800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>5204400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-4153300</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3">
         <v>14800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>-6800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>8500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-57000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>44700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>4300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>15400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-43600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>50700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>41200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>-1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>-4300</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2499500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>969600</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-242900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>530200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>-226300</v>
       </c>
-      <c r="G102" s="3">
-        <v>2377700</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1372000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-509000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>735100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-995000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-927600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>172700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>1885600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-1784800</v>
       </c>
     </row>
